--- a/metingen.xlsx
+++ b/metingen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Test\Documents\GitHub\Bep-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E8BC07-002A-49C0-B256-7860C12C454E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D266D81-C085-4179-9FBC-58875BB70A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE7F35CA-B4C1-43E0-B247-7A3F42EFBD08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="557" xr2:uid="{FE7F35CA-B4C1-43E0-B247-7A3F42EFBD08}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,10 +25,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -411,7 +407,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.2</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="B2">
         <v>5.21</v>
@@ -635,7 +631,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>5.8</v>
+        <v>5.8000000000000007</v>
       </c>
       <c r="B30">
         <v>1.31</v>
@@ -651,7 +647,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>6.2</v>
+        <v>6.2000000000000011</v>
       </c>
       <c r="B32">
         <v>0.97</v>
@@ -675,7 +671,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>6.8</v>
+        <v>6.8000000000000007</v>
       </c>
       <c r="B35">
         <v>0.93</v>
@@ -691,7 +687,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>7.2</v>
+        <v>7.2000000000000011</v>
       </c>
       <c r="B37">
         <v>0.86</v>
@@ -715,7 +711,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>7.8</v>
+        <v>7.8000000000000007</v>
       </c>
       <c r="B40">
         <v>0.65</v>
